--- a/artfynd/A 31335-2021 artfynd.xlsx
+++ b/artfynd/A 31335-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31335-2021 artfynd.xlsx
+++ b/artfynd/A 31335-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68258864</v>
+        <v>68258860</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652758.2282306349</v>
+        <v>652736</v>
       </c>
       <c r="R2" t="n">
-        <v>6601683.928906626</v>
+        <v>6601843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-10-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>68258989</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652790.8487675395</v>
+        <v>652791</v>
       </c>
       <c r="R3" t="n">
-        <v>6601770.073663889</v>
+        <v>6601770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2017-10-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68258844</v>
+        <v>68258864</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652746.9172708543</v>
+        <v>652758</v>
       </c>
       <c r="R4" t="n">
-        <v>6601987.181374418</v>
+        <v>6601684</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2017-10-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68258876</v>
+        <v>68258866</v>
       </c>
       <c r="B5" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,7 +991,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652777.1421436287</v>
+        <v>652783</v>
       </c>
       <c r="R5" t="n">
-        <v>6601756.819077502</v>
+        <v>6601666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2017-10-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68258866</v>
+        <v>68258876</v>
       </c>
       <c r="B6" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1088,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652782.8643099647</v>
+        <v>652777</v>
       </c>
       <c r="R6" t="n">
-        <v>6601666.138157207</v>
+        <v>6601757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2017-10-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68258860</v>
+        <v>68258844</v>
       </c>
       <c r="B7" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652735.9894405934</v>
+        <v>652747</v>
       </c>
       <c r="R7" t="n">
-        <v>6601843.010120632</v>
+        <v>6601987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2017-10-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>68258857</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lejondals naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>652646</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6601882</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
